--- a/data/05_modelado/results/results_otros.xlsx
+++ b/data/05_modelado/results/results_otros.xlsx
@@ -542,52 +542,52 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6997490594988964</v>
+        <v>0.7755728698719533</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01068499371652188</v>
+        <v>0.005642045979370998</v>
       </c>
       <c r="F2" t="n">
-        <v>0.882694998686515</v>
+        <v>0.9205603346469882</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002130639582092924</v>
+        <v>0.003541831237419791</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7841276548612377</v>
+        <v>0.8330307606902737</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6319578076999817</v>
+        <v>0.7256528731751095</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8414631386964728</v>
+        <v>0.8771934502274092</v>
       </c>
       <c r="K2" t="n">
-        <v>8.791</v>
+        <v>6.912</v>
       </c>
       <c r="L2" t="n">
-        <v>5.31</v>
+        <v>6.91</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7244</v>
+        <v>0.7784</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8932</v>
+        <v>0.9273</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.8207</v>
       </c>
       <c r="P2" t="n">
-        <v>0.666</v>
+        <v>0.7402</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8517</v>
+        <v>0.8767</v>
       </c>
       <c r="R2" t="n">
-        <v>0.624</v>
+        <v>0.6933</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7551</v>
+        <v>0.6479</v>
       </c>
     </row>
     <row r="3">
@@ -607,52 +607,52 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6997490594988964</v>
+        <v>0.7755728698719533</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01068499371652188</v>
+        <v>0.005642045979370998</v>
       </c>
       <c r="F3" t="n">
-        <v>0.882694998686515</v>
+        <v>0.9205603346469882</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002130639582092924</v>
+        <v>0.003541831237419791</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7841276548612377</v>
+        <v>0.8330307606902737</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6319578076999817</v>
+        <v>0.7256528731751095</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8414631386964728</v>
+        <v>0.8771934502274092</v>
       </c>
       <c r="K3" t="n">
-        <v>5.851</v>
+        <v>5.686</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7244</v>
+        <v>0.7784</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8932</v>
+        <v>0.9273</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.8207</v>
       </c>
       <c r="P3" t="n">
-        <v>0.666</v>
+        <v>0.7402</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8517</v>
+        <v>0.8767</v>
       </c>
       <c r="R3" t="n">
-        <v>0.624</v>
+        <v>0.6933</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7551</v>
+        <v>0.6479</v>
       </c>
     </row>
     <row r="4">
@@ -672,63 +672,63 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6987706725914837</v>
+        <v>0.7610276129677098</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001943441120628007</v>
+        <v>0.003930919350853034</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8765323572985777</v>
+        <v>0.9165453449080809</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00189915403459892</v>
+        <v>0.002630592056380005</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6173106039839186</v>
+        <v>0.6887434653302952</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8051105415319345</v>
+        <v>0.8503684717731155</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7969957932231292</v>
+        <v>0.8438055469742929</v>
       </c>
       <c r="K4" t="n">
-        <v>11.26</v>
+        <v>13.685</v>
       </c>
       <c r="L4" t="n">
-        <v>5.01</v>
+        <v>6.64</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7116</v>
+        <v>0.7678</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8859</v>
+        <v>0.9235</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6268</v>
+        <v>0.6908</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.8643</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.8471</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5683</v>
+        <v>0.656</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9792</v>
+        <v>0.9113</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GaussianNB</t>
+          <t>BernoulliNB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>smote</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -737,63 +737,63 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6866545587450258</v>
+        <v>0.7209644616533369</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006819172052795935</v>
+        <v>0.005524605109551882</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8529648303212822</v>
+        <v>0.8841486780021585</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004837693111059647</v>
+        <v>0.005967561688845147</v>
       </c>
       <c r="H5" t="n">
-        <v>0.62191207990752</v>
+        <v>0.7132624744453478</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7665892268757002</v>
+        <v>0.7289597892000572</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7953969277466895</v>
+        <v>0.83499391479048</v>
       </c>
       <c r="K5" t="n">
-        <v>1.141</v>
+        <v>0.286</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>6.63</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7023</v>
+        <v>0.7239</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8609</v>
+        <v>0.8875</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6292</v>
+        <v>0.701</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7946</v>
+        <v>0.7483</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.803</v>
+        <v>0.833</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.6044</v>
       </c>
       <c r="S5" t="n">
-        <v>0.596</v>
+        <v>0.4728</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GaussianNB</t>
+          <t>BernoulliNB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -802,63 +802,63 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6755478540484857</v>
+        <v>0.7209644616533369</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009749038200879478</v>
+        <v>0.005524605109551882</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8469549915922656</v>
+        <v>0.8841486780021585</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005025110789714717</v>
+        <v>0.005967561688845147</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6768333234912273</v>
+        <v>0.7132624744453478</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6745464885120654</v>
+        <v>0.7289597892000572</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8105664186278595</v>
+        <v>0.83499391479048</v>
       </c>
       <c r="K6" t="n">
-        <v>4.989</v>
+        <v>0.331</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>6.63</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6875</v>
+        <v>0.7239</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8547</v>
+        <v>0.8875</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6855</v>
+        <v>0.701</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6894</v>
+        <v>0.7483</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8167</v>
+        <v>0.833</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5577</v>
+        <v>0.6044</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5866</v>
+        <v>0.4728</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GaussianNB</t>
+          <t>BernoulliNB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>smote</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -867,58 +867,58 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6755478540484857</v>
+        <v>0.719159332462157</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009749038200879478</v>
+        <v>0.006442997893351844</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8469549915922656</v>
+        <v>0.8834440899523732</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005025110789714717</v>
+        <v>0.006091741210467352</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6768333234912273</v>
+        <v>0.6634652662075602</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6745464885120654</v>
+        <v>0.7851511893443279</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8105664186278595</v>
+        <v>0.8206795392518476</v>
       </c>
       <c r="K7" t="n">
-        <v>4.106</v>
+        <v>2.696</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6875</v>
+        <v>0.7212</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8547</v>
+        <v>0.8868</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6855</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6894</v>
+        <v>0.8043</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8167</v>
+        <v>0.8181</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5577</v>
+        <v>0.5884</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5866</v>
+        <v>0.5286</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BernoulliNB</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -932,58 +932,58 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6321575370589098</v>
+        <v>0.717791033451685</v>
       </c>
       <c r="E8" t="n">
-        <v>0.007691049953674287</v>
+        <v>0.01318829961392401</v>
       </c>
       <c r="F8" t="n">
-        <v>0.829684692324722</v>
+        <v>0.8668456883336573</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006262854064077574</v>
+        <v>0.006217101728968266</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5372733918142222</v>
+        <v>0.6792291950196319</v>
       </c>
       <c r="I8" t="n">
-        <v>0.767988232167509</v>
+        <v>0.7611215629697783</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7386970809654232</v>
+        <v>0.8250666470391879</v>
       </c>
       <c r="K8" t="n">
-        <v>2.167</v>
+        <v>1.685</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6541</v>
+        <v>0.7174</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8466</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5563</v>
+        <v>0.6726</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7936</v>
+        <v>0.7687</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.8229</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4728</v>
+        <v>0.5893</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5427</v>
+        <v>1.068</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BernoulliNB</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -997,58 +997,58 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6340433055736778</v>
+        <v>0.6934780834307281</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006963301764446998</v>
+        <v>0.01257431233199609</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8288793012322191</v>
+        <v>0.8655993475111388</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005686738806756303</v>
+        <v>0.005162576597865669</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6106528813202753</v>
+        <v>0.699957726433367</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6594188299860011</v>
+        <v>0.6872589464364907</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7774016811903098</v>
+        <v>0.8223895764265686</v>
       </c>
       <c r="K9" t="n">
-        <v>0.256</v>
+        <v>5.223</v>
       </c>
       <c r="L9" t="n">
-        <v>5.14</v>
+        <v>6.63</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6562</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8459</v>
+        <v>0.8682</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6313</v>
+        <v>0.6983</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6833</v>
+        <v>0.6919</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7906</v>
+        <v>0.8225</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5061</v>
+        <v>0.5699</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4687</v>
+        <v>1.0734</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BernoulliNB</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1062,52 +1062,52 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6340433055736778</v>
+        <v>0.6934780834307281</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006963301764446998</v>
+        <v>0.01257431233199609</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8288793012322191</v>
+        <v>0.8655993475111388</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005686738806756303</v>
+        <v>0.005162576597865669</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6106528813202753</v>
+        <v>0.699957726433367</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6594188299860011</v>
+        <v>0.6872589464364907</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7774016811903098</v>
+        <v>0.8223895764265686</v>
       </c>
       <c r="K10" t="n">
-        <v>0.143</v>
+        <v>3.378</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>6.63</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6562</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8459</v>
+        <v>0.8682</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6313</v>
+        <v>0.6983</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6833</v>
+        <v>0.6919</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7906</v>
+        <v>0.8225</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5061</v>
+        <v>0.5699</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4687</v>
+        <v>1.0734</v>
       </c>
     </row>
   </sheetData>
